--- a/erp-server/erp-server-wms/src/main/resources/excel/inventoryFlow.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/inventoryFlow.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="21480" windowHeight="12945"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -82,6 +82,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="13"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>SPU</t>
     </r>
     <r>
@@ -124,7 +129,7 @@
     <t>{.sourceCode}</t>
   </si>
   <si>
-    <t>{.operationMode}</t>
+    <t>{.operationModeName}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -1334,7 +1339,9 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="6" width="16.875" customWidth="1"/>
+    <col min="1" max="4" width="16.875" customWidth="1"/>
+    <col min="5" max="5" width="22.375" customWidth="1"/>
+    <col min="6" max="6" width="16.875" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="16.875" customWidth="1"/>
     <col min="9" max="9" width="26.25" customWidth="1"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/inventoryFlow.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/inventoryFlow.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21480" windowHeight="12945"/>
+    <workbookView windowWidth="21240" windowHeight="11265"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
     <t>{.billDate}</t>
   </si>
   <si>
-    <t>{.sourceType}</t>
+    <t>{.sourceTypeName}</t>
   </si>
   <si>
     <t>{.sourceCode}</t>
